--- a/weeks/◆ 2026년 09월 3주 편성표 (0914 ~ 0920).xlsx
+++ b/weeks/◆ 2026년 09월 3주 편성표 (0914 ~ 0920).xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="38">
+  <fonts count="34">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -221,35 +221,11 @@
     <font>
       <name val="Arial"/>
       <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
       <color rgb="001C970F"/>
       <u val="none"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,22 +254,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDFFBD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C1E1FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFDAAE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDFFBD"/>
       </patternFill>
     </fill>
   </fills>
@@ -361,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyNumberFormat="true">
       <alignment wrapText="true"/>
@@ -456,38 +427,26 @@
     <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="28" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="30" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="31" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="32" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="33" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -503,48 +462,48 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.0"/>
-    <col min="2" max="2" customWidth="true" width="0.375"/>
-    <col min="3" max="3" customWidth="true" width="5.125"/>
-    <col min="4" max="4" customWidth="true" width="3.625"/>
-    <col min="5" max="5" customWidth="true" width="2.125"/>
-    <col min="6" max="6" customWidth="true" width="3.625"/>
-    <col min="7" max="7" customWidth="true" width="16.375"/>
-    <col min="8" max="8" customWidth="true" width="0.375"/>
-    <col min="9" max="9" customWidth="true" width="5.125"/>
-    <col min="10" max="10" customWidth="true" width="3.625"/>
-    <col min="11" max="11" customWidth="true" width="2.125"/>
-    <col min="12" max="12" customWidth="true" width="3.625"/>
-    <col min="13" max="13" customWidth="true" width="16.375"/>
-    <col min="14" max="14" customWidth="true" width="0.375"/>
-    <col min="15" max="15" customWidth="true" width="5.125"/>
-    <col min="16" max="16" customWidth="true" width="3.625"/>
-    <col min="17" max="17" customWidth="true" width="2.125"/>
-    <col min="18" max="18" customWidth="true" width="3.625"/>
-    <col min="19" max="19" customWidth="true" width="16.375"/>
-    <col min="20" max="20" customWidth="true" width="0.375"/>
-    <col min="21" max="21" customWidth="true" width="5.125"/>
-    <col min="22" max="22" customWidth="true" width="3.625"/>
-    <col min="23" max="23" customWidth="true" width="2.125"/>
-    <col min="24" max="24" customWidth="true" width="3.625"/>
-    <col min="25" max="25" customWidth="true" width="16.375"/>
-    <col min="26" max="26" customWidth="true" width="0.375"/>
-    <col min="27" max="27" customWidth="true" width="5.125"/>
-    <col min="28" max="28" customWidth="true" width="3.625"/>
-    <col min="29" max="29" customWidth="true" width="2.125"/>
-    <col min="30" max="30" customWidth="true" width="3.625"/>
-    <col min="31" max="31" customWidth="true" width="16.375"/>
-    <col min="32" max="32" customWidth="true" width="0.375"/>
-    <col min="33" max="33" customWidth="true" width="5.125"/>
-    <col min="34" max="34" customWidth="true" width="3.625"/>
-    <col min="35" max="35" customWidth="true" width="2.125"/>
-    <col min="36" max="36" customWidth="true" width="3.625"/>
-    <col min="37" max="37" customWidth="true" width="16.375"/>
-    <col min="38" max="38" customWidth="true" width="0.375"/>
-    <col min="39" max="39" customWidth="true" width="5.125"/>
-    <col min="40" max="40" customWidth="true" width="3.625"/>
-    <col min="41" max="41" customWidth="true" width="2.125"/>
-    <col min="42" max="42" customWidth="true" width="3.625"/>
-    <col min="43" max="43" customWidth="true" width="16.625"/>
+    <col min="2" max="2" customWidth="true" width="0.25"/>
+    <col min="3" max="3" customWidth="true" width="3.75"/>
+    <col min="4" max="4" customWidth="true" width="2.625"/>
+    <col min="5" max="5" customWidth="true" width="1.5"/>
+    <col min="6" max="6" customWidth="true" width="2.625"/>
+    <col min="7" max="7" customWidth="true" width="11.875"/>
+    <col min="8" max="8" customWidth="true" width="0.25"/>
+    <col min="9" max="9" customWidth="true" width="3.75"/>
+    <col min="10" max="10" customWidth="true" width="2.625"/>
+    <col min="11" max="11" customWidth="true" width="1.5"/>
+    <col min="12" max="12" customWidth="true" width="2.625"/>
+    <col min="13" max="13" customWidth="true" width="11.875"/>
+    <col min="14" max="14" customWidth="true" width="0.25"/>
+    <col min="15" max="15" customWidth="true" width="3.75"/>
+    <col min="16" max="16" customWidth="true" width="2.625"/>
+    <col min="17" max="17" customWidth="true" width="1.5"/>
+    <col min="18" max="18" customWidth="true" width="2.625"/>
+    <col min="19" max="19" customWidth="true" width="11.875"/>
+    <col min="20" max="20" customWidth="true" width="0.25"/>
+    <col min="21" max="21" customWidth="true" width="3.75"/>
+    <col min="22" max="22" customWidth="true" width="2.625"/>
+    <col min="23" max="23" customWidth="true" width="1.5"/>
+    <col min="24" max="24" customWidth="true" width="2.625"/>
+    <col min="25" max="25" customWidth="true" width="11.875"/>
+    <col min="26" max="26" customWidth="true" width="0.25"/>
+    <col min="27" max="27" customWidth="true" width="3.75"/>
+    <col min="28" max="28" customWidth="true" width="2.625"/>
+    <col min="29" max="29" customWidth="true" width="1.5"/>
+    <col min="30" max="30" customWidth="true" width="2.625"/>
+    <col min="31" max="31" customWidth="true" width="11.875"/>
+    <col min="32" max="32" customWidth="true" width="0.25"/>
+    <col min="33" max="33" customWidth="true" width="3.75"/>
+    <col min="34" max="34" customWidth="true" width="2.625"/>
+    <col min="35" max="35" customWidth="true" width="1.5"/>
+    <col min="36" max="36" customWidth="true" width="2.625"/>
+    <col min="37" max="37" customWidth="true" width="11.875"/>
+    <col min="38" max="38" customWidth="true" width="0.25"/>
+    <col min="39" max="39" customWidth="true" width="3.75"/>
+    <col min="40" max="40" customWidth="true" width="2.625"/>
+    <col min="41" max="41" customWidth="true" width="1.5"/>
+    <col min="42" max="42" customWidth="true" width="2.625"/>
+    <col min="43" max="43" customWidth="true" width="11.625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="24.75">
@@ -591,7 +550,7 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>1차 확정안입니다.</t>
+          <t>확정 편성표입니다.</t>
         </is>
       </c>
       <c r="AM1" s="4"/>
@@ -1034,7 +993,7 @@
       </c>
       <c r="AN8" s="24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AO8" s="24" t="inlineStr">
@@ -1070,19 +1029,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="F9" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>해즈픽 칫솔</t>
         </is>
       </c>
       <c r="H9" s="25"/>
@@ -1113,7 +1073,7 @@
         </is>
       </c>
       <c r="N9" s="25"/>
-      <c r="O9" s="33" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t>06:15</t>
         </is>
@@ -1123,19 +1083,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="Q9" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="R9" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="S9" s="34" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="S9" s="30" t="inlineStr">
+        <is>
+          <t>일월매트</t>
         </is>
       </c>
       <c r="T9" s="25"/>
@@ -1144,7 +1105,7 @@
           <t>06:15</t>
         </is>
       </c>
-      <c r="V9" s="35" t="inlineStr">
+      <c r="V9" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1156,12 +1117,12 @@
       </c>
       <c r="X9" s="30" t="inlineStr">
         <is>
-          <t>'잡화'</t>
-        </is>
-      </c>
-      <c r="Y9" s="36" t="inlineStr">
-        <is>
-          <t>키플링 가방모음전</t>
+          <t>'패션2Lab'</t>
+        </is>
+      </c>
+      <c r="Y9" s="33" t="inlineStr">
+        <is>
+          <t>][AnD] 에이앤디 26FW 보머 니트 자켓 1종</t>
         </is>
       </c>
       <c r="Z9" s="25"/>
@@ -1220,12 +1181,12 @@
       <c r="AL9" s="25"/>
       <c r="AM9" s="29" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AN9" s="24" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AO9" s="24" t="inlineStr">
@@ -1336,7 +1297,7 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="V10" s="35" t="inlineStr">
+      <c r="V10" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1351,7 +1312,7 @@
           <t>'잡화'</t>
         </is>
       </c>
-      <c r="Y10" s="36" t="inlineStr">
+      <c r="Y10" s="33" t="inlineStr">
         <is>
           <t>스케쳐스 맥스쿠셔닝 아우라</t>
         </is>
@@ -1503,7 +1464,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="32" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1518,7 +1479,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="S11" s="36" t="inlineStr">
+      <c r="S11" s="33" t="inlineStr">
         <is>
           <t>라이317 코듀로이팬츠1종</t>
         </is>
@@ -1541,12 +1502,12 @@
       </c>
       <c r="X11" s="30" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
+          <t>P.D.Lab</t>
         </is>
       </c>
       <c r="Y11" s="30" t="inlineStr">
         <is>
-          <t>디아루체 26 FW 3도 스트라이프 헨리넥 니트 3종</t>
+          <t>알레보밥용기</t>
         </is>
       </c>
       <c r="Z11" s="25"/>
@@ -1555,7 +1516,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="AB11" s="35" t="inlineStr">
+      <c r="AB11" s="32" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1570,7 +1531,7 @@
           <t>'패션1Lab'</t>
         </is>
       </c>
-      <c r="AE11" s="36" t="inlineStr">
+      <c r="AE11" s="33" t="inlineStr">
         <is>
           <t>프리마클라쎄 양모 베스트</t>
         </is>
@@ -1581,7 +1542,7 @@
           <t>08:20</t>
         </is>
       </c>
-      <c r="AH11" s="35" t="inlineStr">
+      <c r="AH11" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1596,7 +1557,7 @@
           <t>'건강식품2'</t>
         </is>
       </c>
-      <c r="AK11" s="36" t="inlineStr">
+      <c r="AK11" s="33" t="inlineStr">
         <is>
           <t>콤비타 로렌지</t>
         </is>
@@ -1646,19 +1607,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>'일반식품1'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
         <is>
-          <t>[명절]신세계 꽃갈비원육</t>
+          <t>파머시안 PDRN크림</t>
         </is>
       </c>
       <c r="H12" s="25"/>
@@ -1693,7 +1655,7 @@
           <t>09:05</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1708,13 +1670,13 @@
           <t>'패션4Lab'</t>
         </is>
       </c>
-      <c r="S12" s="36" t="inlineStr">
+      <c r="S12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">라일앤스콧 </t>
         </is>
       </c>
       <c r="T12" s="25"/>
-      <c r="U12" s="33" t="inlineStr">
+      <c r="U12" s="29" t="inlineStr">
         <is>
           <t>09:25</t>
         </is>
@@ -1726,17 +1688,17 @@
       </c>
       <c r="W12" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="X12" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="Y12" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'일반식품1'</t>
+        </is>
+      </c>
+      <c r="Y12" s="30" t="inlineStr">
+        <is>
+          <t>[명절]신세계 꽃갈비원육</t>
         </is>
       </c>
       <c r="Z12" s="25"/>
@@ -1745,7 +1707,7 @@
           <t>09:05</t>
         </is>
       </c>
-      <c r="AB12" s="35" t="inlineStr">
+      <c r="AB12" s="32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1760,7 +1722,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="AE12" s="36" t="inlineStr">
+      <c r="AE12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에바큐브꾸띄르 26FW 자카드 플리츠 가디건 </t>
         </is>
@@ -1771,7 +1733,7 @@
           <t>09:20</t>
         </is>
       </c>
-      <c r="AH12" s="35" t="inlineStr">
+      <c r="AH12" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1786,7 +1748,7 @@
           <t>멀티커머스</t>
         </is>
       </c>
-      <c r="AK12" s="36" t="inlineStr">
+      <c r="AK12" s="33" t="inlineStr">
         <is>
           <t>지방시 쿠션</t>
         </is>
@@ -1883,7 +1845,7 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P13" s="32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1898,7 +1860,7 @@
           <t>'잡화'</t>
         </is>
       </c>
-      <c r="S13" s="36" t="inlineStr">
+      <c r="S13" s="33" t="inlineStr">
         <is>
           <t>베르만 투어랩 프로 캐리어</t>
         </is>
@@ -1914,20 +1876,19 @@
           <t>70</t>
         </is>
       </c>
-      <c r="W13" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="W13" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="X13" s="30" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'패션2Lab'</t>
         </is>
       </c>
       <c r="Y13" s="30" t="inlineStr">
         <is>
-          <t>해즈픽 칫솔</t>
+          <t>디아루체 26 FW 3도 스트라이프 헨리넥 니트 3종</t>
         </is>
       </c>
       <c r="Z13" s="25"/>
@@ -1936,7 +1897,7 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AB13" s="35" t="inlineStr">
+      <c r="AB13" s="32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1951,7 +1912,7 @@
           <t>'패션1Lab'</t>
         </is>
       </c>
-      <c r="AE13" s="36" t="inlineStr">
+      <c r="AE13" s="33" t="inlineStr">
         <is>
           <t>고비 캐시미어 48수 베이직 풀오버</t>
         </is>
@@ -1962,7 +1923,7 @@
           <t>10:20</t>
         </is>
       </c>
-      <c r="AH13" s="35" t="inlineStr">
+      <c r="AH13" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1977,7 +1938,7 @@
           <t>'건강식품1'</t>
         </is>
       </c>
-      <c r="AK13" s="36" t="inlineStr">
+      <c r="AK13" s="33" t="inlineStr">
         <is>
           <t>임페리얼 넛츠 리저브</t>
         </is>
@@ -2043,29 +2004,30 @@
         </is>
       </c>
       <c r="H14" s="25"/>
-      <c r="I14" s="33" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>11:35</t>
         </is>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K14" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="L14" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="M14" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'주얼리'</t>
+        </is>
+      </c>
+      <c r="M14" s="30" t="inlineStr">
+        <is>
+          <t>한민24K주얼리</t>
         </is>
       </c>
       <c r="N14" s="25"/>
@@ -2074,7 +2036,7 @@
           <t>10:25</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr">
+      <c r="P14" s="34" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -2089,7 +2051,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="S14" s="30" t="inlineStr">
+      <c r="S14" s="35" t="inlineStr">
         <is>
           <t>[명절]신세계 꽃갈비원육</t>
         </is>
@@ -2153,7 +2115,7 @@
           <t>11:20</t>
         </is>
       </c>
-      <c r="AH14" s="35" t="inlineStr">
+      <c r="AH14" s="32" t="inlineStr">
         <is>
           <t>85</t>
         </is>
@@ -2168,7 +2130,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="AK14" s="36" t="inlineStr">
+      <c r="AK14" s="33" t="inlineStr">
         <is>
           <t>구찌_크로스백</t>
         </is>
@@ -2236,7 +2198,7 @@
       <c r="H15" s="25"/>
       <c r="I15" s="29" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J15" s="24" t="inlineStr">
@@ -2265,122 +2227,121 @@
           <t>11:35</t>
         </is>
       </c>
-      <c r="P15" s="24" t="inlineStr">
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q15" s="31" t="inlineStr">
+      <c r="Q15" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="R15" s="30" t="inlineStr">
+        <is>
+          <t>'일반식품1'</t>
+        </is>
+      </c>
+      <c r="S15" s="35" t="inlineStr">
+        <is>
+          <t>[명절]두리담 송편</t>
+        </is>
+      </c>
+      <c r="T15" s="25"/>
+      <c r="U15" s="29" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W15" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="X15" s="30" t="inlineStr">
+        <is>
+          <t>'뷰티1'</t>
+        </is>
+      </c>
+      <c r="Y15" s="30" t="inlineStr">
+        <is>
+          <t>태극제약 도미나스 NMN세럼</t>
+        </is>
+      </c>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="29" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AB15" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC15" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AD15" s="30" t="inlineStr">
+        <is>
+          <t>'레포츠'</t>
+        </is>
+      </c>
+      <c r="AE15" s="30" t="inlineStr">
+        <is>
+          <t>아이그너 26FW</t>
+        </is>
+      </c>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="29" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AH15" s="32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AI15" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AJ15" s="30" t="inlineStr">
+        <is>
+          <t>'노블레스'</t>
+        </is>
+      </c>
+      <c r="AK15" s="33" t="inlineStr">
+        <is>
+          <t>미우미우_숄더백</t>
+        </is>
+      </c>
+      <c r="AL15" s="25"/>
+      <c r="AM15" s="29" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AO15" s="31" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="R15" s="30" t="inlineStr">
-        <is>
-          <t>'주얼리'</t>
-        </is>
-      </c>
-      <c r="S15" s="30" t="inlineStr">
-        <is>
-          <t>한민24K주얼리</t>
-        </is>
-      </c>
-      <c r="T15" s="25"/>
-      <c r="U15" s="29" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W15" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="X15" s="30" t="inlineStr">
-        <is>
-          <t>'뷰티1'</t>
-        </is>
-      </c>
-      <c r="Y15" s="30" t="inlineStr">
-        <is>
-          <t>태극제약 도미나스 NMN세럼</t>
-        </is>
-      </c>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="29" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AB15" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AC15" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="AD15" s="30" t="inlineStr">
-        <is>
-          <t>'레포츠'</t>
-        </is>
-      </c>
-      <c r="AE15" s="30" t="inlineStr">
-        <is>
-          <t>아이그너 26FW</t>
-        </is>
-      </c>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="29" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AH15" s="35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AI15" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="AJ15" s="30" t="inlineStr">
-        <is>
-          <t>'노블레스'</t>
-        </is>
-      </c>
-      <c r="AK15" s="36" t="inlineStr">
-        <is>
-          <t>미우미우_숄더백</t>
-        </is>
-      </c>
-      <c r="AL15" s="25"/>
-      <c r="AM15" s="29" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AO15" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
-        </is>
-      </c>
       <c r="AP15" s="30" t="inlineStr">
         <is>
           <t>'리빙'</t>
@@ -2388,7 +2349,7 @@
       </c>
       <c r="AQ15" s="30" t="inlineStr">
         <is>
-          <t>루나앤슬립 고주파 스프레드 3종</t>
+          <t>플로너스 디퓨저 추석스페셜</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2388,12 @@
       <c r="H16" s="25"/>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="J16" s="24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K16" s="24" t="inlineStr">
@@ -2445,13 +2406,13 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="M16" s="38" t="inlineStr">
+      <c r="M16" s="36" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
       </c>
       <c r="N16" s="25"/>
-      <c r="O16" s="33" t="inlineStr">
+      <c r="O16" s="29" t="inlineStr">
         <is>
           <t>12:35</t>
         </is>
@@ -2468,12 +2429,12 @@
       </c>
       <c r="R16" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="S16" s="34" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="S16" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="T16" s="25"/>
@@ -2497,7 +2458,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="Y16" s="38" t="inlineStr">
+      <c r="Y16" s="36" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2510,23 +2471,22 @@
       </c>
       <c r="AB16" s="24" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AC16" s="31" t="inlineStr">
-        <is>
-          <t>수
-수</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC16" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="AD16" s="30" t="inlineStr">
         <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="AE16" s="30" t="inlineStr">
-        <is>
-          <t>테팔 그릴</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="AE16" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="AF16" s="25"/>
@@ -2567,20 +2527,19 @@
           <t>75</t>
         </is>
       </c>
-      <c r="AO16" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AP16" s="30" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
+          <t>'리빙'</t>
         </is>
       </c>
       <c r="AQ16" s="30" t="inlineStr">
         <is>
-          <t>리브이셀 레티콜라겐 마스크팩</t>
+          <t>니카사 진공흡착 스팀다리미 시즌2</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2570,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2655,17 +2614,17 @@
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="R17" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="S17" s="38" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'건강식품1'</t>
+        </is>
+      </c>
+      <c r="S17" s="30" t="inlineStr">
+        <is>
+          <t>셀렉티드 메이플 정과세트</t>
         </is>
       </c>
       <c r="T17" s="25"/>
@@ -2698,17 +2657,17 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AB17" s="24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AC17" s="31" t="inlineStr">
         <is>
-          <t>중
+          <t>수
 수</t>
         </is>
       </c>
@@ -2719,7 +2678,7 @@
       </c>
       <c r="AE17" s="30" t="inlineStr">
         <is>
-          <t>한일 보이스믹서기</t>
+          <t>테팔 그릴</t>
         </is>
       </c>
       <c r="AF17" s="25"/>
@@ -2833,7 +2792,7 @@
       </c>
       <c r="M18" s="30" t="inlineStr">
         <is>
-          <t>칼만 밧드</t>
+          <t>한일 보이스믹서기</t>
         </is>
       </c>
       <c r="N18" s="25"/>
@@ -2900,20 +2859,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC18" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AC18" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AD18" s="30" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
+          <t>'일반식품1'</t>
         </is>
       </c>
       <c r="AE18" s="30" t="inlineStr">
         <is>
-          <t>가히 캐비어 PDRN 앰플</t>
+          <t>제주 그린향</t>
         </is>
       </c>
       <c r="AF18" s="25"/>
@@ -2927,20 +2885,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI18" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AI18" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="AJ18" s="30" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
-        </is>
-      </c>
-      <c r="AK18" s="30" t="inlineStr">
-        <is>
-          <t>파머시안 PDRN크림</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="AK18" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="AL18" s="25"/>
@@ -2954,20 +2911,19 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO18" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AP18" s="30" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'잡화'</t>
         </is>
       </c>
       <c r="AQ18" s="30" t="inlineStr">
         <is>
-          <t>플로너스 디퓨저 추석스페셜</t>
+          <t>슈올즈 포브</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3007,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="S19" s="38" t="inlineStr">
+      <c r="S19" s="36" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3064,22 +3020,23 @@
       </c>
       <c r="V19" s="24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W19" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="W19" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="X19" s="30" t="inlineStr">
         <is>
-          <t>'일반식품1'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="Y19" s="30" t="inlineStr">
         <is>
-          <t>거창 홍로</t>
+          <t>가히 캐비어 PDRN 앰플</t>
         </is>
       </c>
       <c r="Z19" s="25"/>
@@ -3106,7 +3063,7 @@
       </c>
       <c r="AE19" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">칼만 통3중 저압냄비 </t>
+          <t>칼만 밧드</t>
         </is>
       </c>
       <c r="AF19" s="25"/>
@@ -3174,7 +3131,7 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -3189,7 +3146,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G20" s="39" t="inlineStr">
+      <c r="G20" s="37" t="inlineStr">
         <is>
           <t>김규흔 한과세트</t>
         </is>
@@ -3217,7 +3174,7 @@
       </c>
       <c r="M20" s="30" t="inlineStr">
         <is>
-          <t>[명절]두리담 송편</t>
+          <t>거창 홍로</t>
         </is>
       </c>
       <c r="N20" s="25"/>
@@ -3226,30 +3183,31 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="P20" s="35" t="inlineStr">
+      <c r="P20" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q20" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="Q20" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="R20" s="30" t="inlineStr">
         <is>
-          <t>'일반식품1'</t>
-        </is>
-      </c>
-      <c r="S20" s="36" t="inlineStr">
-        <is>
-          <t>제주 그린향</t>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="S20" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칼만 통3중 저압냄비 </t>
         </is>
       </c>
       <c r="T20" s="25"/>
       <c r="U20" s="29" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="V20" s="24" t="inlineStr">
@@ -3265,12 +3223,12 @@
       </c>
       <c r="X20" s="30" t="inlineStr">
         <is>
-          <t>'액티브라이프'</t>
+          <t>'리빙'</t>
         </is>
       </c>
       <c r="Y20" s="30" t="inlineStr">
         <is>
-          <t>디캔트 장어 추석선물세트</t>
+          <t>짐샌더슨 롤러백</t>
         </is>
       </c>
       <c r="Z20" s="25"/>
@@ -3326,7 +3284,7 @@
         </is>
       </c>
       <c r="AL20" s="25"/>
-      <c r="AM20" s="33" t="inlineStr">
+      <c r="AM20" s="29" t="inlineStr">
         <is>
           <t>19:25</t>
         </is>
@@ -3338,17 +3296,17 @@
       </c>
       <c r="AO20" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="AP20" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AQ20" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'일반식품1'</t>
+        </is>
+      </c>
+      <c r="AQ20" s="30" t="inlineStr">
+        <is>
+          <t>[명절]신세계 꽃갈비 원육</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3322,7 @@
           <t>17:40</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -3379,7 +3337,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G21" s="39" t="inlineStr">
+      <c r="G21" s="37" t="inlineStr">
         <is>
           <t>[명절]박정수 새우</t>
         </is>
@@ -3390,7 +3348,7 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="J21" s="35" t="inlineStr">
+      <c r="J21" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3405,7 +3363,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M21" s="39" t="inlineStr">
+      <c r="M21" s="30" t="inlineStr">
         <is>
           <t>수산대전-이보은 왕특대 박대(G월화가능)</t>
         </is>
@@ -3416,7 +3374,7 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="P21" s="35" t="inlineStr">
+      <c r="P21" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3431,7 +3389,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="S21" s="36" t="inlineStr">
+      <c r="S21" s="33" t="inlineStr">
         <is>
           <t>(G)안유성 보리굴비(첫)</t>
         </is>
@@ -3439,12 +3397,12 @@
       <c r="T21" s="25"/>
       <c r="U21" s="29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="V21" s="24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>55</t>
         </is>
       </c>
       <c r="W21" s="31" t="inlineStr">
@@ -3469,7 +3427,7 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="AB21" s="35" t="inlineStr">
+      <c r="AB21" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3484,9 +3442,9 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="AE21" s="36" t="inlineStr">
-        <is>
-          <t>수산대전-제주 옥돔(G 16,18가능)</t>
+      <c r="AE21" s="33" t="inlineStr">
+        <is>
+          <t>(수산대전)제주은갈치</t>
         </is>
       </c>
       <c r="AF21" s="25"/>
@@ -3495,7 +3453,7 @@
           <t>18:35</t>
         </is>
       </c>
-      <c r="AH21" s="35" t="inlineStr">
+      <c r="AH21" s="32" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -3511,7 +3469,7 @@
           <t>'해외여행'</t>
         </is>
       </c>
-      <c r="AK21" s="36" t="inlineStr">
+      <c r="AK21" s="33" t="inlineStr">
         <is>
           <t>롯데관광 장가계</t>
         </is>
@@ -3537,7 +3495,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AQ21" s="38" t="inlineStr">
+      <c r="AQ21" s="36" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3570,7 +3528,7 @@
           <t>'GA'</t>
         </is>
       </c>
-      <c r="G22" s="32" t="inlineStr">
+      <c r="G22" s="36" t="inlineStr">
         <is>
           <t>#금융GA</t>
         </is>
@@ -3660,7 +3618,7 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="AB22" s="35" t="inlineStr">
+      <c r="AB22" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3675,7 +3633,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="AE22" s="36" t="inlineStr">
+      <c r="AE22" s="33" t="inlineStr">
         <is>
           <t>[명절]조선호텔 LA갈비</t>
         </is>
@@ -3746,7 +3704,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>75</t>
         </is>
@@ -3761,7 +3719,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G23" s="39" t="inlineStr">
+      <c r="G23" s="37" t="inlineStr">
         <is>
           <t>황쇼-농협 안심한우</t>
         </is>
@@ -3772,7 +3730,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="J23" s="35" t="inlineStr">
+      <c r="J23" s="32" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -3787,7 +3745,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M23" s="39" t="inlineStr">
+      <c r="M23" s="37" t="inlineStr">
         <is>
           <t>오감쇼-오월식당 보리굴비</t>
         </is>
@@ -3798,7 +3756,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="P23" s="35" t="inlineStr">
+      <c r="P23" s="32" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -3813,7 +3771,7 @@
           <t>언더웨어</t>
         </is>
       </c>
-      <c r="S23" s="36" t="inlineStr">
+      <c r="S23" s="33" t="inlineStr">
         <is>
           <t>콘치웨어 웰니스룩</t>
         </is>
@@ -3910,20 +3868,19 @@
           <t>65</t>
         </is>
       </c>
-      <c r="AO23" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AP23" s="30" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'주얼리'</t>
         </is>
       </c>
       <c r="AQ23" s="30" t="inlineStr">
         <is>
-          <t>니카사 진공흡착 스팀다리미 시즌2</t>
+          <t>골드라벨 24K</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3896,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3954,7 +3911,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G24" s="39" t="inlineStr">
+      <c r="G24" s="37" t="inlineStr">
         <is>
           <t>황쇼-안유성 전복장</t>
         </is>
@@ -3965,7 +3922,7 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="J24" s="35" t="inlineStr">
+      <c r="J24" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3980,7 +3937,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M24" s="39" t="inlineStr">
+      <c r="M24" s="37" t="inlineStr">
         <is>
           <t>오감쇼-화춘옥 갈빗살</t>
         </is>
@@ -3991,7 +3948,7 @@
           <t>20:05</t>
         </is>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -4006,7 +3963,7 @@
           <t>'패션3Lab'</t>
         </is>
       </c>
-      <c r="S24" s="36" t="inlineStr">
+      <c r="S24" s="33" t="inlineStr">
         <is>
           <t>스노야 베이비알파카 터틀넥 外</t>
         </is>
@@ -4113,7 +4070,7 @@
           <t>'GA'</t>
         </is>
       </c>
-      <c r="AQ24" s="38" t="inlineStr">
+      <c r="AQ24" s="36" t="inlineStr">
         <is>
           <t>#금융GA</t>
         </is>
@@ -4131,7 +4088,7 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -4146,7 +4103,7 @@
           <t>'액티브라이프'</t>
         </is>
       </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>황쇼-라베키아 발사믹</t>
         </is>
@@ -4157,7 +4114,7 @@
           <t>21:15</t>
         </is>
       </c>
-      <c r="J25" s="35" t="inlineStr">
+      <c r="J25" s="32" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -4172,7 +4129,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M25" s="39" t="inlineStr">
+      <c r="M25" s="37" t="inlineStr">
         <is>
           <t>오감쇼-화과방 4색 송편</t>
         </is>
@@ -4183,7 +4140,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="P25" s="35" t="inlineStr">
+      <c r="P25" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -4198,7 +4155,7 @@
           <t>'뷰티1'</t>
         </is>
       </c>
-      <c r="S25" s="36" t="inlineStr">
+      <c r="S25" s="33" t="inlineStr">
         <is>
           <t>쿼드쎼라 펜타</t>
         </is>
@@ -4256,29 +4213,30 @@
         </is>
       </c>
       <c r="AF25" s="25"/>
-      <c r="AG25" s="33" t="inlineStr">
+      <c r="AG25" s="29" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="AH25" s="35" t="inlineStr">
+      <c r="AH25" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AI25" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
+      <c r="AI25" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AJ25" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AK25" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'뷰티브랜드'</t>
+        </is>
+      </c>
+      <c r="AK25" s="33" t="inlineStr">
+        <is>
+          <t>약손명가 약손명가 올리라밴드</t>
         </is>
       </c>
       <c r="AL25" s="25"/>
@@ -4320,7 +4278,7 @@
           <t>22:25</t>
         </is>
       </c>
-      <c r="D26" s="35" t="inlineStr">
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -4335,7 +4293,7 @@
           <t>'액티브라이프'</t>
         </is>
       </c>
-      <c r="G26" s="39" t="inlineStr">
+      <c r="G26" s="37" t="inlineStr">
         <is>
           <t>황쇼-대천 곱창캔김</t>
         </is>
@@ -4405,20 +4363,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W26" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="W26" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
         </is>
       </c>
       <c r="X26" s="30" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
+          <t>'잡화'</t>
         </is>
       </c>
       <c r="Y26" s="30" t="inlineStr">
         <is>
-          <t>랑벨 앰플</t>
+          <t>사업부P-르무통 스위트 메리제인</t>
         </is>
       </c>
       <c r="Z26" s="25"/>
@@ -4427,7 +4384,7 @@
           <t>22:40</t>
         </is>
       </c>
-      <c r="AB26" s="35" t="inlineStr">
+      <c r="AB26" s="32" t="inlineStr">
         <is>
           <t>115</t>
         </is>
@@ -4442,7 +4399,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="AE26" s="36" t="inlineStr">
+      <c r="AE26" s="33" t="inlineStr">
         <is>
           <t>프라다_크로스백</t>
         </is>
@@ -4458,19 +4415,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI26" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="AI26" s="31" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="AJ26" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="AK26" s="38" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="AK26" s="30" t="inlineStr">
+        <is>
+          <t>락앤락 원터치</t>
         </is>
       </c>
       <c r="AL26" s="25"/>
@@ -4503,17 +4461,17 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>'레포츠'</t>
-        </is>
-      </c>
-      <c r="G27" s="30" t="inlineStr">
-        <is>
-          <t>라스튜디오 양가죽 자켓</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="G27" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="H27" s="25"/>
@@ -4555,17 +4513,17 @@
       </c>
       <c r="Q27" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="R27" s="30" t="inlineStr">
         <is>
-          <t>'GA'</t>
-        </is>
-      </c>
-      <c r="S27" s="38" t="inlineStr">
-        <is>
-          <t>#금융GA</t>
+          <t>'레포츠'</t>
+        </is>
+      </c>
+      <c r="S27" s="30" t="inlineStr">
+        <is>
+          <t>라스튜디오 양가죽 자켓</t>
         </is>
       </c>
       <c r="T27" s="25"/>
@@ -4586,42 +4544,42 @@
       </c>
       <c r="X27" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="Y27" s="38" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'GA'</t>
+        </is>
+      </c>
+      <c r="Y27" s="36" t="inlineStr">
+        <is>
+          <t>#금융GA</t>
         </is>
       </c>
       <c r="Z27" s="25"/>
-      <c r="AA27" s="33" t="inlineStr">
+      <c r="AA27" s="29" t="inlineStr">
         <is>
           <t>00:35</t>
         </is>
       </c>
-      <c r="AB27" s="35" t="inlineStr">
+      <c r="AB27" s="32" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
       <c r="AC27" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>수</t>
         </is>
       </c>
       <c r="AD27" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE27" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'잡화'</t>
+        </is>
+      </c>
+      <c r="AE27" s="33" t="inlineStr">
+        <is>
+          <t>MBB 아테나 크루즈백</t>
         </is>
       </c>
       <c r="AF27" s="25"/>
-      <c r="AG27" s="33" t="inlineStr">
+      <c r="AG27" s="29" t="inlineStr">
         <is>
           <t>00:30</t>
         </is>
@@ -4631,15 +4589,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI27" s="24"/>
+      <c r="AI27" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
       <c r="AJ27" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AK27" s="37" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AK27" s="30" t="inlineStr">
+        <is>
+          <t>오토드다리미</t>
         </is>
       </c>
       <c r="AL27" s="25"/>
@@ -4670,19 +4632,20 @@
           <t>65</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="G28" s="32" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'뷰티1'</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>토리든 앰플</t>
         </is>
       </c>
       <c r="H28" s="25"/>
@@ -4723,24 +4686,23 @@
           <t>65</t>
         </is>
       </c>
-      <c r="Q28" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="Q28" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="R28" s="30" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
-        </is>
-      </c>
-      <c r="S28" s="30" t="inlineStr">
-        <is>
-          <t>토리든 앰플</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="S28" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="T28" s="25"/>
-      <c r="U28" s="40" t="inlineStr">
+      <c r="U28" s="38" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
@@ -4840,7 +4802,7 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="D29" s="41" t="inlineStr">
+      <c r="D29" s="34" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -4855,7 +4817,7 @@
           <t>'건강식품2'</t>
         </is>
       </c>
-      <c r="G29" s="42" t="inlineStr">
+      <c r="G29" s="35" t="inlineStr">
         <is>
           <t>그레인온 캡슐레이션효소</t>
         </is>
@@ -4965,7 +4927,7 @@
           <t>01:30</t>
         </is>
       </c>
-      <c r="D30" s="41" t="inlineStr">
+      <c r="D30" s="34" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -4980,7 +4942,7 @@
           <t>'건강식품2'</t>
         </is>
       </c>
-      <c r="G30" s="42" t="inlineStr">
+      <c r="G30" s="35" t="inlineStr">
         <is>
           <t>보넬드 당근주스</t>
         </is>
